--- a/output/full_scan/batch_seq1_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-05.xlsx
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>231.855170900669</v>
+        <v>231.8551709006689</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>13.35</v>

--- a/output/full_scan/batch_seq1_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-05.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1326</v>
+        <v>1560</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>825.5074210307712</v>
+        <v>1074.003072784667</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>1040</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.8279883337685</v>
+        <v>79.4872063453212</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.49141017596029</v>
+        <v>44.28394479441122</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.9988176158365332</v>
+        <v>0.55929716017378</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.08605308832395139</v>
+        <v>17.21692596231129</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1569</v>
+        <v>1303</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>793.2329512120886</v>
+        <v>1011.548439334258</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>68.5</v>
+        <v>286</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>78.2983983917905</v>
+        <v>73.6314766988549</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>59.9661785043403</v>
+        <v>31.16956156385637</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.923295121208853</v>
+        <v>1.342272097363369</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.9831704397581192</v>
+        <v>2.875665012718388</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1303</v>
+        <v>1326</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>716.5484393342574</v>
+        <v>955.5074210307712</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>286</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.63147670010446</v>
+        <v>59.82798828216806</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31.16956167016003</v>
+        <v>28.49140989435775</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.342272097363369</v>
+        <v>0.9988176158365332</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.875665012373425</v>
+        <v>0.08605308859099201</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1315</v>
+        <v>1569</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>672.4264444676744</v>
+        <v>933.2329512120886</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>70.11991973234774</v>
+        <v>78.29839855836863</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>41.6721841024976</v>
+        <v>59.96617862328991</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.900656713205339</v>
+        <v>1.923295121208853</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.08031757310518629</v>
+        <v>0.9831704391127448</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1560</v>
+        <v>1459</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>654.0030727846676</v>
+        <v>807.3840786527105</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1040</v>
+        <v>20.55</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>79.48720632627868</v>
+        <v>91.52608941053634</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>44.28394479441121</v>
+        <v>57.27439931607097</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.55929716017378</v>
+        <v>4.838407865271057</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>17.21692596342403</v>
+        <v>0.3615592722846943</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>643.5441186393349</v>
+        <v>803.5441186393344</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>68.5</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.63274499978816</v>
+        <v>62.63274493447876</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.15528750325536</v>
+        <v>25.15528751126012</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.01187507319006</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2246866682479376</v>
+        <v>0.2246866685261141</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1416</v>
+        <v>1513</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>639.8298167756801</v>
+        <v>697.6181346490506</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11.85</v>
+        <v>166.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.15137929558445</v>
+        <v>52.04127726778206</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15.70162177586702</v>
+        <v>9.689576316278206</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.677963613789666</v>
+        <v>1.104763515617247</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0458877937534551</v>
+        <v>0.1451531969362807</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1312</v>
+        <v>1101</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>618.0164651210799</v>
+        <v>692.8065924411087</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>52.83530222616197</v>
+        <v>52.0206233731715</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>40.91651652643282</v>
+        <v>38.8052601228551</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.496206487917301</v>
+        <v>1.009799318411898</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0862858349965774</v>
+        <v>0.0730679888094085</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1101</v>
+        <v>1439</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>617.8065924411087</v>
+        <v>691.0533768675497</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>25</v>
+        <v>29.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>52.02062723688405</v>
+        <v>56.95251115892673</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38.80526014963792</v>
+        <v>17.62339923112383</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.009799318411898</v>
+        <v>0.174506394685179</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0730679887760269</v>
+        <v>0.0216429589832877</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1528</v>
+        <v>1315</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>617.2912105859871</v>
+        <v>672.4264444676744</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>24.15</v>
+        <v>68.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.79611042361962</v>
+        <v>70.11991964110226</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.43590717864165</v>
+        <v>41.67218408602652</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3252490158965637</v>
+        <v>1.900656713205339</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0971991045393156</v>
+        <v>0.0803175731274452</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1558</v>
+        <v>1409</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>615.0621457850117</v>
+        <v>668.0853682959602</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>110</v>
+        <v>25.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.96943937264265</v>
+        <v>56.27318043690117</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>39.8284535569863</v>
+        <v>14.9613538974258</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.528872138449875</v>
+        <v>1.449070440494943</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.3891081266516836</v>
+        <v>0.0597056210966086</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1418</v>
+        <v>1310</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>608.1418571956059</v>
+        <v>647.595437793677</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.7</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>65.72268103644419</v>
+        <v>63.54092338618218</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.36539337595706</v>
+        <v>36.23100123041925</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9342782313973194</v>
+        <v>1.064938081390641</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1198668122093278</v>
+        <v>0.0829948103455021</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1459</v>
+        <v>1528</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>607.3840786527105</v>
+        <v>647.2912105859872</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>20.55</v>
+        <v>24.15</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>91.52608941246008</v>
+        <v>55.7961102897151</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>57.27439934471145</v>
+        <v>39.43590726137833</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4.838407865271057</v>
+        <v>0.3252490158965637</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3615592722656249</v>
+        <v>-0.0971991041721196</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1313</v>
+        <v>1416</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>598.7924225857473</v>
+        <v>639.8298167756801</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12.5</v>
+        <v>11.85</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.74878375828908</v>
+        <v>64.15137923351452</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.24474437945393</v>
+        <v>15.70162177263543</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.239924560220179</v>
+        <v>1.677963613789666</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0378503773020283</v>
+        <v>0.0458877937645821</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1456</v>
+        <v>1312</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>589.7556451723646</v>
+        <v>618.0164651210799</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14.85</v>
+        <v>14.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.47647796655544</v>
+        <v>52.83530216796809</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.88181195409725</v>
+        <v>40.91651657167648</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3636051978812953</v>
+        <v>0.496206487917301</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0810819114689999</v>
+        <v>-0.0862858349164613</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>582.0248007602523</v>
+        <v>615.0621457850117</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.49984723716314</v>
+        <v>57.96943935912737</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>37.37798414298248</v>
+        <v>39.82845358549664</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6518300941890057</v>
+        <v>0.528872138449875</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.2287807779270898</v>
+        <v>-0.3891081266739329</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1439</v>
+        <v>1418</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>576.0533768675497</v>
+        <v>608.1418571956059</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>29.3</v>
+        <v>18.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>56.95251113844562</v>
+        <v>65.72268148513864</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.62339925271587</v>
+        <v>30.36539339418746</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.174506394685179</v>
+        <v>0.9342782313973194</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0216429590166685</v>
+        <v>0.1198668120424179</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1323</v>
+        <v>1563</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>568.8623682595312</v>
+        <v>602.0248007602523</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21.55</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.21937352849806</v>
+        <v>63.49984732456205</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.32426245643813</v>
+        <v>37.37798418783622</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.745611573978067</v>
+        <v>0.6518300941890057</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0184998780925099</v>
+        <v>-0.2287807783084954</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1409</v>
+        <v>1313</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>523.0853682959601</v>
+        <v>598.7924225857478</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>25.3</v>
+        <v>12.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.27318030443769</v>
+        <v>59.74878365241727</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14.96135391177676</v>
+        <v>28.24474428072327</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.449070440494943</v>
+        <v>1.239924560220179</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0597056210854832</v>
+        <v>0.0378503773843695</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1568</v>
+        <v>1456</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>509.4168236592432</v>
+        <v>589.7556451723646</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>31.45</v>
+        <v>14.85</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.39054302430756</v>
+        <v>58.47647799350043</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.7041944777133</v>
+        <v>21.88181196409565</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.154410503947883</v>
+        <v>0.3636051978812953</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.2158157508959043</v>
+        <v>0.08108191144674599</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1513</v>
+        <v>1568</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>507.6181346490508</v>
+        <v>584.4168236592431</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>166.5</v>
+        <v>31.45</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.04127718730368</v>
+        <v>56.39054299773308</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9.689576207259771</v>
+        <v>27.70419444633109</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.104763515617247</v>
+        <v>1.154410503947883</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1451531974926275</v>
+        <v>0.2158157509181604</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>507.5954377936768</v>
+        <v>568.8623682595312</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>21.55</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.5409234478639</v>
+        <v>56.21937351150176</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>36.23100120274144</v>
+        <v>14.32426275515503</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.064938081390641</v>
+        <v>1.745611573978067</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.08299481030544439</v>
+        <v>-0.0184998780813814</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1220</v>
+        <v>1441</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>483.0915952234424</v>
+        <v>563.3627306084779</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10.95</v>
+        <v>9.81</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.02153947819321</v>
+        <v>66.02497697053602</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19.3957233959794</v>
+        <v>25.66497825009698</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.626166902113112</v>
+        <v>0.6686384691415411</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0259152153855957</v>
+        <v>0.1334365000183789</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1314</v>
+        <v>1220</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>479.8385955589713</v>
+        <v>483.0915952234424</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8.67</v>
+        <v>10.95</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.10842322541345</v>
+        <v>57.02153941542642</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>42.68847078123515</v>
+        <v>19.39572339625112</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9623879255779068</v>
+        <v>1.626166902113112</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0034581787421993</v>
+        <v>0.0259152153855957</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>468.7121664147934</v>
+        <v>479.8385955589713</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>14.3</v>
+        <v>8.67</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.29423657280693</v>
+        <v>53.10842316641452</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.25597727212461</v>
+        <v>42.68847074995681</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8339720379828895</v>
+        <v>0.9623879255779068</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0053908582710666</v>
+        <v>0.0034581787711284</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1339</v>
+        <v>1308</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>468.7057692573104</v>
+        <v>468.7121664147934</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>42.7</v>
+        <v>14.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>44.83638941773754</v>
+        <v>52.29423645081738</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.56217017430102</v>
+        <v>31.25597718924312</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.304154799428308</v>
+        <v>0.8339720379828895</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0371806807376304</v>
+        <v>-0.0053908581486687</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1213</v>
+        <v>1339</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>444.5976226829403</v>
+        <v>468.7057692573104</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>7.2</v>
+        <v>42.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.13443040963273</v>
+        <v>44.83638952444582</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9.205350153415177</v>
+        <v>23.5621702785289</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.1823217370920551</v>
+        <v>1.304154799428308</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.014929379906574</v>
+        <v>0.0371806805484641</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1539</v>
+        <v>1213</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>439.2376655705175</v>
+        <v>444.59762268294</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15.65</v>
+        <v>7.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.15012076167869</v>
+        <v>51.13443042532946</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.5620555974924</v>
+        <v>9.205350153814802</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.528151497498775</v>
+        <v>0.1823217370920551</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0200405488426074</v>
+        <v>0.0149293798398114</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1455</v>
+        <v>1539</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>438.9963675376776</v>
+        <v>439.2376655705175</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>15.65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>51.98478492739939</v>
+        <v>50.15012093809221</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.8256150216936</v>
+        <v>24.5620556054986</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.190522163683006</v>
+        <v>1.528151497498775</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0046751825182146</v>
+        <v>0.0200405488092261</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1434</v>
+        <v>1455</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>434.1885703858553</v>
+        <v>438.9963675376776</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>17.85</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.50996582240678</v>
+        <v>51.98478486167739</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.58619213444145</v>
+        <v>25.82561503148313</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.356242937306269</v>
+        <v>1.190522163683006</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0113242461258091</v>
+        <v>0.0046751825382424</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>430.7850198156106</v>
+        <v>437.8957401854398</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25.7</v>
+        <v>13.75</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.07221344931186</v>
+        <v>48.85456710763629</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.0180978669434</v>
+        <v>13.70474160349141</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4736934559738672</v>
+        <v>0.4959955462938329</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0606488925618509</v>
+        <v>0.0425680415921584</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1338</v>
+        <v>1434</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>418.7259988046616</v>
+        <v>434.1885703858553</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>14.95</v>
+        <v>17.85</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.33399544837074</v>
+        <v>48.5099657395487</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>36.27642431155001</v>
+        <v>23.58619237722302</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.134257904695028</v>
+        <v>1.356242937306269</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1069111680223253</v>
+        <v>0.0113242461814455</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1474</v>
+        <v>1521</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>410.6402434450857</v>
+        <v>430.7850198156104</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.98</v>
+        <v>25.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>47.55348797189417</v>
+        <v>53.07220759709049</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.13817330253307</v>
+        <v>31.0180965813818</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.045109861793831</v>
+        <v>0.4736934559738672</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0101218025583947</v>
+        <v>0.0606488981699262</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1473</v>
+        <v>1340</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>406.0276539088553</v>
+        <v>424.5438372272607</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>19.1</v>
+        <v>5.22</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>24.88915181239486</v>
+        <v>51.31723126851479</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>36.92590760039732</v>
+        <v>13.29267944765053</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.002765390885526</v>
+        <v>1.038263025330624</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0574381378331543</v>
+        <v>0.0045202302237579</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1309</v>
+        <v>1541</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>397.9562438766824</v>
+        <v>418.9485797940955</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>14.05</v>
+        <v>20.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.6433197606117</v>
+        <v>51.20212024702145</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.07026772592874</v>
+        <v>18.5511329155394</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7230469540119213</v>
+        <v>1.824710315209465</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0216045682296292</v>
+        <v>0.4599632260588157</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1304</v>
+        <v>1338</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>396.9402124268304</v>
+        <v>418.7259988046617</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>12.6</v>
+        <v>14.95</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.98661584148845</v>
+        <v>53.33399539889355</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.43496170715939</v>
+        <v>36.27642431155001</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7116931641405019</v>
+        <v>1.134257904695028</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0295790612217573</v>
+        <v>0.1069111680000715</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1467</v>
+        <v>1304</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>396.4707303703677</v>
+        <v>416.9402124268289</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>49.59582654646715</v>
+        <v>53.98661571155016</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.45821983545883</v>
+        <v>26.43496171764222</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.261850290043659</v>
+        <v>0.7116931641405019</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0585973108731798</v>
+        <v>0.0295790613664109</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1441</v>
+        <v>1474</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>393.3627306084779</v>
+        <v>410.6402434450857</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>9.81</v>
+        <v>9.98</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>66.02497689422449</v>
+        <v>47.5534879128661</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25.66497827979458</v>
+        <v>23.13817357051725</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6686384691415411</v>
+        <v>4.045109861793831</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1334365000890085</v>
+        <v>0.0101218025583947</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1210</v>
+        <v>1102</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>383.0817553609581</v>
+        <v>409.2853183516369</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>51.6</v>
+        <v>35.15</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.02222281617939</v>
+        <v>50.20584267899022</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.9876588649173</v>
+        <v>24.40596021864188</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.198710002481602</v>
+        <v>0.7150154654293583</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0321014601895969</v>
+        <v>-0.0536833304506231</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1341</v>
+        <v>1473</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>376.0293254557572</v>
+        <v>406.0276539088553</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>59.4</v>
+        <v>19.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.91371132591177</v>
+        <v>24.88915188129049</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9.628230768746096</v>
+        <v>36.92590762882254</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.941052631578948</v>
+        <v>2.002765390885526</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.39268695579942</v>
+        <v>-0.0574381378442802</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1225</v>
+        <v>1309</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>376.015303825466</v>
+        <v>397.9562438766824</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>24.35</v>
+        <v>14.05</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>43.77420040648083</v>
+        <v>54.64331969645684</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.96007762272948</v>
+        <v>30.07026770042661</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.697326891310847</v>
+        <v>0.7230469540119213</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0065289714191083</v>
+        <v>0.0216045683075166</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>372.2924373330853</v>
+        <v>396.4707303703677</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>24.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.72356299041984</v>
+        <v>49.59582646756161</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9.1033020440253</v>
+        <v>13.45821984605294</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4154406426588201</v>
+        <v>2.261850290043659</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0207646958602687</v>
+        <v>0.0585973109221401</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>369.5311416327611</v>
+        <v>392.073682879874</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>69</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.42667229582744</v>
+        <v>46.17452686248809</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>29.22816162800529</v>
+        <v>12.20290980505876</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7067734492010574</v>
+        <v>1.021373682804245</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,11 +2796,11 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0080869386503303</v>
+        <v>-0.09736126790380049</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>367.7112162484171</v>
+        <v>387.7112162484171</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>99.8</v>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>41.16948191883131</v>
+        <v>41.16948193275537</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.29355892497392</v>
+        <v>19.29355888158563</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.26507649606747</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0480316342994333</v>
+        <v>0.0480316341436468</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1463</v>
+        <v>1210</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>367.4188266748317</v>
+        <v>383.0817553609581</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>17.5</v>
+        <v>51.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.73149727886414</v>
+        <v>42.02222287719075</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.06251387115866</v>
+        <v>24.98765889377612</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2621022145916792</v>
+        <v>1.198710002481602</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0093328492887152</v>
+        <v>0.0321014600783289</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1414</v>
+        <v>1319</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>357.6575015308268</v>
+        <v>376.8329421709777</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>17.3</v>
+        <v>77.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>39.68335592866458</v>
+        <v>41.79209276357366</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.08241390991149</v>
+        <v>14.90785167555361</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7549886067305808</v>
+        <v>0.9506654088903348</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0482728455870508</v>
+        <v>-0.2279031471070692</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1103</v>
+        <v>1341</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>352.229451244408</v>
+        <v>376.0293254557572</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>13.05</v>
+        <v>59.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45.10543115278033</v>
+        <v>51.91371132740528</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24.03030856618396</v>
+        <v>9.628230772486877</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6628562898856901</v>
+        <v>1.941052631578948</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0051553570172882</v>
+        <v>1.392686955732664</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1582</v>
+        <v>1225</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>340.0278067097464</v>
+        <v>376.015303825466</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>24.35</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.82676206538365</v>
+        <v>43.77420033381561</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.44811387913284</v>
+        <v>22.96007763682006</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.744794080842629</v>
+        <v>1.697326891310847</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2977524544165069</v>
+        <v>-0.0065289714747455</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1477</v>
+        <v>1470</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>334.6936649624706</v>
+        <v>372.2924373330853</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>197.5</v>
+        <v>24.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.84684304546344</v>
+        <v>51.72356201313067</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27.56281569273134</v>
+        <v>9.103301217419729</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.708969612879863</v>
+        <v>0.4154406426588201</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.9475416221120848</v>
+        <v>0.020764700400139</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1102</v>
+        <v>1538</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>334.2853183516368</v>
+        <v>371.6544408583026</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>35.15</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.20584258501567</v>
+        <v>57.75388694027873</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.40596016507537</v>
+        <v>12.30161487339299</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7150154654293583</v>
+        <v>0.1707044913199287</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0536833303949854</v>
+        <v>0.7541939217205146</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1440</v>
+        <v>1506</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>323.5153619800228</v>
+        <v>369.5311416327611</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>13.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.52921634885345</v>
+        <v>42.42667233946283</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12.01730551411843</v>
+        <v>29.22816162800529</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.113527333101811</v>
+        <v>0.7067734492010574</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0056321205278821</v>
+        <v>0.0080869386503303</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1516</v>
+        <v>1463</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>322.8957401854399</v>
+        <v>367.4188266748317</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>13.75</v>
+        <v>17.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.85456712877366</v>
+        <v>49.73149730448316</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.70474160349141</v>
+        <v>16.06251387115866</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4959955462938329</v>
+        <v>0.2621022145916792</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0425680415921584</v>
+        <v>0.0093328492775871</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1437</v>
+        <v>1582</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>316.5266125915884</v>
+        <v>360.0278067097464</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>31.25</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>37.66600839725585</v>
+        <v>52.82676200517056</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.48036375457235</v>
+        <v>19.44811388967581</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.185027150360809</v>
+        <v>1.744794080842629</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1716768791433878</v>
+        <v>0.2977524545055348</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1340</v>
+        <v>1414</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>314.5438372272607</v>
+        <v>357.6575015308267</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>5.22</v>
+        <v>17.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.31723130057791</v>
+        <v>39.68335571410142</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.29267944765053</v>
+        <v>27.08241390991149</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.038263025330624</v>
+        <v>0.7549886067305808</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0045202302259832</v>
+        <v>0.0482728457205414</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1475</v>
+        <v>1218</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>314.3848269286204</v>
+        <v>354.6681750177734</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.1</v>
+        <v>14.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.137902537035</v>
+        <v>48.49218915660876</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.31590363507122</v>
+        <v>4.656410413670728</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8317476062268467</v>
+        <v>0.7439526786432999</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0128422052484795</v>
+        <v>0.0269081373447174</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>312.4148134929742</v>
+        <v>352.229451244408</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>13.2</v>
+        <v>13.05</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>31.21580881994018</v>
+        <v>45.10543121803685</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>40.62639993740115</v>
+        <v>24.03030859239131</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.120201484146616</v>
+        <v>0.6628562898856901</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0042112283193782</v>
+        <v>0.0051553569950334</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1527</v>
+        <v>1402</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>307.5043264048869</v>
+        <v>338.2418667130834</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>32.8</v>
+        <v>27.75</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>53.98529657791836</v>
+        <v>45.09305959702638</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13.96709132897019</v>
+        <v>11.06500519251469</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.001733418483715</v>
+        <v>0.780432613682701</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.06566044528090879</v>
+        <v>-0.0406933783459764</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1464</v>
+        <v>1477</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>307.3770963418698</v>
+        <v>334.6936649624706</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9.93</v>
+        <v>197.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>38.34556157519118</v>
+        <v>52.84684311656542</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.98303459353004</v>
+        <v>27.56281572854327</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.79697341502401</v>
+        <v>1.708969612879863</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0110626679911344</v>
+        <v>0.9475416213331852</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1307</v>
+        <v>1440</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>304.0186502622893</v>
+        <v>323.515361980023</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>30.85</v>
+        <v>13.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.51315581292715</v>
+        <v>49.52921625425326</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.28288252932825</v>
+        <v>12.01730556265442</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.375691936391238</v>
+        <v>1.113527333101811</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1004689930932636</v>
+        <v>-0.0056321204499921</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1517</v>
+        <v>1231</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>301.6325171088279</v>
+        <v>319.1790686654529</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>10.25</v>
+        <v>78.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>35.69055570930301</v>
+        <v>34.39275962078176</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.99671992057001</v>
+        <v>11.73027838473924</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.713425857271213</v>
+        <v>2.809578292671485</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0104769102424074</v>
+        <v>0.0271057620349851</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1524</v>
+        <v>1437</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>297.0245085337426</v>
+        <v>316.5266125915884</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>25.8</v>
+        <v>31.25</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>37.4940810929311</v>
+        <v>37.66600859224759</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>30.7350339004164</v>
+        <v>13.48036416487001</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.542192111199711</v>
+        <v>1.185027150360809</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0053959306419559</v>
+        <v>-0.1716768793548033</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1537</v>
+        <v>1514</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>291.93443716759</v>
+        <v>314.5021491962481</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>113.5</v>
+        <v>102</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>31.82468185644668</v>
+        <v>49.04601437638431</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>33.65817393818305</v>
+        <v>12.8014817314843</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.207495686036629</v>
+        <v>1.142840897738479</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2062231058909118</v>
+        <v>0.1718634152884388</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1236</v>
+        <v>1475</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>285.5516335158549</v>
+        <v>314.3848269286204</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.5841623594599</v>
+        <v>48.13790255262524</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.81522867320276</v>
+        <v>21.31590359891259</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.355440847907197</v>
+        <v>0.8317476062268467</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0431456027506043</v>
+        <v>0.0128422050481909</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1514</v>
+        <v>1109</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>284.5021491962481</v>
+        <v>312.4148134929744</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>102</v>
+        <v>13.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.04601437638431</v>
+        <v>31.21580881994018</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.80148164079383</v>
+        <v>40.62639998508897</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.142840897738479</v>
+        <v>1.120201484146616</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1718634156222521</v>
+        <v>-0.0042112283305065</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1504</v>
+        <v>1527</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>282.0736828798742</v>
+        <v>307.5043264048867</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>69</v>
+        <v>32.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.17452678497317</v>
+        <v>53.98529675958972</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.20290981094828</v>
+        <v>13.96709163634134</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.021373682804245</v>
+        <v>1.001733418483715</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0973612677257672</v>
+        <v>0.0656604451028699</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1443</v>
+        <v>1464</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>281.5231564695624</v>
+        <v>307.3770963418698</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>23.05</v>
+        <v>9.93</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.85786287004285</v>
+        <v>38.3455612294882</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5.931162441302659</v>
+        <v>22.98303460084505</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.035251736855648</v>
+        <v>0.79697341502401</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.009515121681371801</v>
+        <v>0.0110626680022604</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1529</v>
+        <v>1307</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>279.7098574977228</v>
+        <v>304.0186502622892</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>15.65</v>
+        <v>30.85</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.26530661056689</v>
+        <v>49.51315589044101</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.33170588156448</v>
+        <v>13.28288256310379</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8312894061620181</v>
+        <v>2.375691936391238</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1060726103359588</v>
+        <v>0.1004689931043882</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1476</v>
+        <v>1517</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>275.9354215792206</v>
+        <v>301.6325171088279</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>278.5</v>
+        <v>10.25</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>34.36958660351917</v>
+        <v>35.69055538150346</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>43.06870508283723</v>
+        <v>21.9967199917895</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.300181870775708</v>
+        <v>1.713425857271213</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.8245607962548416</v>
+        <v>0.0104769103425507</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1233</v>
+        <v>1524</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>275.2389884905626</v>
+        <v>297.0245085337385</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>28</v>
+        <v>25.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.48158476421751</v>
+        <v>37.49408089383144</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.56320566397428</v>
+        <v>30.7350339004164</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4521102688807253</v>
+        <v>1.542192111199711</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0055875703934482</v>
+        <v>0.0053959306753393</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1442</v>
+        <v>1476</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>271.7566465217311</v>
+        <v>295.9354215792205</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26.1</v>
+        <v>278.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>28.11879084783524</v>
+        <v>34.36958659136575</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>29.46634443049216</v>
+        <v>43.06870506289276</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7797614107637844</v>
+        <v>1.300181870775708</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.4697655238683121</v>
+        <v>0.8245607973675657</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1216</v>
+        <v>1537</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>270.9234788177665</v>
+        <v>291.93443716759</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>72.7</v>
+        <v>113.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>34.59027273487918</v>
+        <v>31.82468185644668</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.26016260897656</v>
+        <v>33.65817393818305</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.112929131591882</v>
+        <v>1.207495686036629</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2068397076343957</v>
+        <v>0.2062231058909118</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1460</v>
+        <v>1236</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>266.8422426918077</v>
+        <v>285.5516335158549</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>6.12</v>
+        <v>25.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>26.54422966254398</v>
+        <v>48.58416255666124</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>24.47504065300764</v>
+        <v>16.81522885378821</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.443911078822299</v>
+        <v>1.355440847907197</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0091870326213226</v>
+        <v>-0.0431456027728587</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1319</v>
+        <v>1443</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>266.8329421709777</v>
+        <v>281.5231564695624</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>77.8</v>
+        <v>23.05</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>41.79209290036264</v>
+        <v>45.85786288068945</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.90785167555361</v>
+        <v>5.931162427125662</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9506654088903348</v>
+        <v>1.035251736855648</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2279031471070692</v>
+        <v>0.0095151216591189</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1402</v>
+        <v>1529</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>263.2418667130835</v>
+        <v>279.7098574977227</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>27.75</v>
+        <v>15.65</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.09305953284446</v>
+        <v>44.26530634997125</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.06500521125046</v>
+        <v>23.33170586834593</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.780432613682701</v>
+        <v>0.8312894061620181</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0406933782792142</v>
+        <v>0.1060726105028627</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1305</v>
+        <v>1233</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>261.4221207532094</v>
+        <v>275.2389884905626</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.35</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>53.92193740000089</v>
+        <v>47.48158476421751</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.61659513927422</v>
+        <v>13.56320567257594</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8532477749056482</v>
+        <v>0.4521102688807253</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0355504962917732</v>
+        <v>0.0055875703934482</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1201</v>
+        <v>1442</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>256.0154873452746</v>
+        <v>271.7566465217304</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11.4</v>
+        <v>26.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>30.97100607550492</v>
+        <v>28.11879092262573</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>41.81495553297811</v>
+        <v>29.46634446356524</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6635279667579549</v>
+        <v>0.7797614107637844</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0326969250524414</v>
+        <v>-0.4697655240685979</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4555,21 +4555,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>254.6790857111708</v>
+        <v>270.9234788177665</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>42.5</v>
+        <v>72.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.11777218135714</v>
+        <v>34.59027272037989</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.85976149943341</v>
+        <v>13.26016261495665</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.650026592191726</v>
+        <v>1.112929131591882</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0442751536850234</v>
+        <v>-0.2068397076343957</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1436</v>
+        <v>1460</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>245.724273247036</v>
+        <v>266.8422426918077</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>35.6</v>
+        <v>6.12</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>38.87967347243692</v>
+        <v>26.54422966254398</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.44823436834884</v>
+        <v>24.47504065300764</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.040244389528183</v>
+        <v>1.443911078822299</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.091355975756347</v>
+        <v>-0.0091870326235475</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1227</v>
+        <v>1201</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>245.2478584952608</v>
+        <v>256.0154873452746</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>27.75</v>
+        <v>11.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>34.19173111476196</v>
+        <v>30.97100615852473</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.84994283417504</v>
+        <v>41.81495553297812</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.083793937407415</v>
+        <v>0.6635279667579549</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0161919041112423</v>
+        <v>-0.0326969250524414</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1218</v>
+        <v>1203</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>244.6681750177733</v>
+        <v>254.6790857111708</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>14.4</v>
+        <v>42.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.49218922949975</v>
+        <v>42.11777220875452</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.65641038696532</v>
+        <v>10.85976152049548</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7439526786432999</v>
+        <v>1.650026592191726</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0269081373224616</v>
+        <v>-0.0442751536405162</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1231</v>
+        <v>1305</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>244.1790686654525</v>
+        <v>251.4221207532093</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>78.5</v>
+        <v>12.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>34.39275944580115</v>
+        <v>53.92193726162455</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.73027844933524</v>
+        <v>16.61659499178015</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.809578292671485</v>
+        <v>0.8532477749056482</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0271057622575401</v>
+        <v>0.0355504964030452</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1447</v>
+        <v>1436</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>242.5335752468564</v>
+        <v>245.724273247036</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>6.41</v>
+        <v>35.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.84216082232489</v>
+        <v>38.87967350198478</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.8112973796554</v>
+        <v>18.44823435915276</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.122764727347105</v>
+        <v>1.040244389528183</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0222923990423921</v>
+        <v>-0.0913559758231141</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1465</v>
+        <v>1227</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>240.6393839077494</v>
+        <v>245.2478584952599</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>11.65</v>
+        <v>27.75</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.27246794688092</v>
+        <v>34.19173122269459</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.18209952711262</v>
+        <v>15.84994283878402</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5726247977678258</v>
+        <v>2.083793937407415</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0153834176760303</v>
+        <v>-0.0161919042113874</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1531</v>
+        <v>1447</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>232.9630683059556</v>
+        <v>242.5335752468563</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>11.45</v>
+        <v>6.41</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>32.54207634092236</v>
+        <v>42.84216081098035</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.74700224191369</v>
+        <v>15.8112973851725</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9093120603067066</v>
+        <v>1.122764727347105</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0177883533032962</v>
+        <v>0.0222923990557447</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1446</v>
+        <v>1465</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>231.8551709006689</v>
+        <v>240.6393839077494</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>13.35</v>
+        <v>11.65</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.19226048695192</v>
+        <v>41.27246802350267</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.49222487507256</v>
+        <v>21.18209961036554</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6170537798938812</v>
+        <v>0.5726247977678258</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0080057249705322</v>
+        <v>0.0153834176649024</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1468</v>
+        <v>1531</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>229</v>
+        <v>232.9630683059556</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>13.15</v>
+        <v>11.45</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.52944877328657</v>
+        <v>32.54207632298676</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>10.33885261853275</v>
+        <v>17.74700224191369</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>5.386263015753562</v>
+        <v>0.9093120603067066</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0149804467470915</v>
+        <v>0.0177883533032962</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1423</v>
+        <v>1446</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>222.8310192235697</v>
+        <v>231.8551709006689</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>34.5</v>
+        <v>13.35</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.98952286445318</v>
+        <v>40.19226164008595</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>9.19802697125338</v>
+        <v>19.49222489796276</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3163758123233229</v>
+        <v>0.6170537798938812</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.4991415749983506</v>
+        <v>0.0080057249594043</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1457</v>
+        <v>1468</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>218.9790131179772</v>
+        <v>229</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>14.3</v>
+        <v>13.15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.32091193230609</v>
+        <v>48.5294488102698</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.40706201425061</v>
+        <v>10.33885264157031</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.453958310931541</v>
+        <v>5.386263015753562</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0153619913783652</v>
+        <v>0.0149804467359637</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1541</v>
+        <v>1423</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>218.9485797940955</v>
+        <v>222.8310192235697</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>20.6</v>
+        <v>34.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.20212024002306</v>
+        <v>50.98952286164374</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.55113287064434</v>
+        <v>9.19802693575266</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.824710315209465</v>
+        <v>0.3163758123233229</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.459963226147829</v>
+        <v>0.4991415750539819</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1451</v>
+        <v>1503</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>217.588886065374</v>
+        <v>220.0532560491713</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.52930100014532</v>
+        <v>44.31217137976589</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.98430051607884</v>
+        <v>8.732597222020196</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.743642580134009</v>
+        <v>0.9085331368008336</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0001092605365248</v>
+        <v>-0.0994439756237057</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1232</v>
+        <v>1457</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>213.34728680658</v>
+        <v>218.9790131179768</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>153.5</v>
+        <v>14.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.15391056202722</v>
+        <v>45.3209119984343</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.9678293922479</v>
+        <v>15.40706187546742</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7255924804533129</v>
+        <v>1.453958310931541</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2211036608351271</v>
+        <v>-0.0153619914006182</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1410</v>
+        <v>1451</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>213.303090962477</v>
+        <v>217.588886065374</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>24.05</v>
+        <v>17</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.76017389928456</v>
+        <v>41.5293009191678</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6.617149697890446</v>
+        <v>19.98430054369264</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3445811517034374</v>
+        <v>1.743642580134009</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0154848755877936</v>
+        <v>-0.0001092605365248</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1321</v>
+        <v>1229</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>212.3084658636215</v>
+        <v>217.3407797347816</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>32.3</v>
+        <v>39.65</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.61163428934252</v>
+        <v>38.71250080116033</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8.342943754592465</v>
+        <v>18.61136645898051</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9078860441440856</v>
+        <v>0.9912750295218736</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0270348123020546</v>
+        <v>-0.0592587556016853</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1515</v>
+        <v>1232</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>206.0271667237363</v>
+        <v>213.34728680658</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.7</v>
+        <v>153.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.59423017764957</v>
+        <v>43.1539106114986</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7.238716998785484</v>
+        <v>11.96782937101295</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.258900176943671</v>
+        <v>0.7255924804533129</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0130587409742439</v>
+        <v>-0.2211036608351271</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1472</v>
+        <v>1410</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>205.3415592786325</v>
+        <v>213.303090962477</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>24.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>52.19885743288317</v>
+        <v>41.76017366298592</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8.359429528982909</v>
+        <v>6.617149676374769</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.334676744990166</v>
+        <v>0.3445811517034374</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>1.454859520075922</v>
+        <v>0.0154848756323004</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1519</v>
+        <v>1325</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>198.4380193700813</v>
+        <v>212.5508377839253</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>691</v>
+        <v>25.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>42.88045004604936</v>
+        <v>48.14818288233557</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.27993740206271</v>
+        <v>17.50328490255743</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9027110828674668</v>
+        <v>1.139476877717596</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-2.405135549310636</v>
+        <v>0.027348461416319</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1419</v>
+        <v>1321</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>195.2579006820553</v>
+        <v>212.3084658636215</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>65.3</v>
+        <v>32.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.29520924005686</v>
+        <v>47.61163435505904</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8.69170700448583</v>
+        <v>8.342943754592469</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6263987171889707</v>
+        <v>0.9078860441440856</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1128995953422196</v>
+        <v>-0.0270348123465607</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1453</v>
+        <v>1515</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>194.5154032699602</v>
+        <v>206.0271667237363</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>10.9</v>
+        <v>28.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.25556197024879</v>
+        <v>39.59423016347846</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.67542337925548</v>
+        <v>7.238717018496501</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.798341111874813</v>
+        <v>1.258900176943671</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0056766888409125</v>
+        <v>-0.0130587409742439</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1215</v>
+        <v>1472</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>194.2076688289807</v>
+        <v>205.3415592786296</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>104</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>37.33636024381125</v>
+        <v>52.19885743691007</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.17077721747092</v>
+        <v>8.359429579609117</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9936262272564704</v>
+        <v>1.334676744990166</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2855168077624239</v>
+        <v>1.454859520098187</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1256</v>
+        <v>1519</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>190.736080291844</v>
+        <v>198.4380193700813</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>168</v>
+        <v>691</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.48520613750814</v>
+        <v>42.88045004604936</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>7.537863007959811</v>
+        <v>11.27993741868678</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6145512217561157</v>
+        <v>0.9027110828674668</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.11913516117191</v>
+        <v>-2.405135551981212</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1108</v>
+        <v>1419</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>185.094442774803</v>
+        <v>195.2579006820548</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>11.05</v>
+        <v>65.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>30.93384554097787</v>
+        <v>44.2952089983742</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>48.64554813573118</v>
+        <v>8.691706926591715</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4123498124113072</v>
+        <v>0.6263987171889707</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0299924871491742</v>
+        <v>-0.1128995948971171</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1316</v>
+        <v>1453</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>185.0265628224617</v>
+        <v>194.5154032699602</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.36300116102002</v>
+        <v>45.25556193822057</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.34840909736589</v>
+        <v>14.67542339655058</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.107125551186162</v>
+        <v>1.798341111874813</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0417763531553822</v>
+        <v>0.0056766888409125</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>183.7151142174357</v>
+        <v>194.2076688289737</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>104</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.73996080384058</v>
+        <v>37.33635990783835</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.62548246554791</v>
+        <v>14.17077746527354</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.153915124216668</v>
+        <v>0.9936262272564704</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.007963351239595601</v>
+        <v>-0.2855168065384421</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1110</v>
+        <v>1256</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>175.5589835350886</v>
+        <v>190.736080291844</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14.35</v>
+        <v>168</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>26.5745981066277</v>
+        <v>38.48520608884873</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>33.5126226630313</v>
+        <v>7.537863033616787</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5682936923542007</v>
+        <v>0.6145512217561157</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1042571455990831</v>
+        <v>0.1191351610606292</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1540</v>
+        <v>1108</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>173.0472748160048</v>
+        <v>185.094442774803</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>18.95</v>
+        <v>11.05</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>37.0865649045685</v>
+        <v>30.93384459438116</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>12.4950749034479</v>
+        <v>48.64554916357633</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.694922914655693</v>
+        <v>0.4123498124113072</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0132301723825928</v>
+        <v>0.0299924872938268</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1536</v>
+        <v>1316</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>171.6719703543178</v>
+        <v>185.0265628224617</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>46.1</v>
+        <v>10.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>37.93711858404257</v>
+        <v>42.36301055547219</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>8.383163207456509</v>
+        <v>19.34840913375141</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.187544200657749</v>
+        <v>1.107125551186162</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0620495216354859</v>
+        <v>-0.0417763560373078</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1538</v>
+        <v>1217</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>171.654440858302</v>
+        <v>183.7151142174357</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>57.75388692700639</v>
+        <v>40.73996090759503</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.30161493800228</v>
+        <v>12.62548258224173</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1707044913199287</v>
+        <v>1.153915124216668</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.7541939217761502</v>
+        <v>-0.007963351239595601</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1324</v>
+        <v>1110</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>171.1757613030284</v>
+        <v>175.5589835350887</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>9.91</v>
+        <v>14.35</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.74866271620668</v>
+        <v>26.57459796177936</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.74779014889434</v>
+        <v>33.51262272899655</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.871425550339828</v>
+        <v>0.5682936923542007</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0039388667640129</v>
+        <v>-0.1042571455768287</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1413</v>
+        <v>1540</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>170.7353540597693</v>
+        <v>173.0472748160049</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9.1</v>
+        <v>18.95</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.87278669165022</v>
+        <v>37.0865649753071</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8.873833701007349</v>
+        <v>12.4950749034479</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.005462568555509</v>
+        <v>1.694922914655693</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0047688178547769</v>
+        <v>-0.0132301723714658</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>167.3335751676383</v>
+        <v>171.6719703543179</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14.85</v>
+        <v>46.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.68705062574542</v>
+        <v>37.93711852343465</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.39175509357662</v>
+        <v>8.383163254007743</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7342217752074428</v>
+        <v>1.187544200657749</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0667906573849277</v>
+        <v>0.0620495218135197</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1532</v>
+        <v>1324</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>165.3206496124985</v>
+        <v>171.1757613030285</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>21.65</v>
+        <v>9.91</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>31.94470506808407</v>
+        <v>41.74866262788287</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.23808395304645</v>
+        <v>14.74779020210324</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2.431931514576873</v>
+        <v>1.871425550339828</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.085770862735761</v>
+        <v>-0.0039388667640129</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1444</v>
+        <v>1413</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>164.468258659126</v>
+        <v>170.7353540597693</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.10482364998943</v>
+        <v>43.87278680491588</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.89224264722588</v>
+        <v>8.873833744422575</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.981207602685119</v>
+        <v>1.005462568555509</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0205414285161863</v>
+        <v>-0.0047688178770308</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1471</v>
+        <v>1526</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>160.6944069787253</v>
+        <v>167.3335751676383</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>14.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.14330283795743</v>
+        <v>41.68705041440026</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>12.43727799432824</v>
+        <v>20.39175541649438</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.471904545674222</v>
+        <v>0.7342217752074428</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0090199927157392</v>
+        <v>0.06679065747394369</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.0132160981143</v>
+        <v>165.3206496124985</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>30.2</v>
+        <v>21.65</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.39520772738828</v>
+        <v>31.94470500333823</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.69248620302907</v>
+        <v>16.23808404026335</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.379052545818205</v>
+        <v>2.431931514576873</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0677903255064323</v>
+        <v>-0.085770862735761</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1417</v>
+        <v>1444</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>157.4545696507094</v>
+        <v>164.468258659126</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.78550212337299</v>
+        <v>43.10482356906852</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>23.48663001471197</v>
+        <v>17.89224267076949</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.191606764802882</v>
+        <v>0.981207602685119</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0182534089102118</v>
+        <v>0.0205414285495669</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1435</v>
+        <v>1471</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>148.2684549892786</v>
+        <v>160.6944069787251</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>21.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>49.63658294202291</v>
+        <v>46.1433026855075</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6.797353868196433</v>
+        <v>12.43727800969054</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.9753150353875368</v>
+        <v>1.471904545674222</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1922640011877086</v>
+        <v>0.0090199927491212</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>146.0196992075363</v>
+        <v>158.0132160981143</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>26.7</v>
+        <v>30.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>36.87335914839496</v>
+        <v>39.39520767154928</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>21.12722707412601</v>
+        <v>14.6924861877384</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.9660150962722694</v>
+        <v>1.379052545818205</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0100445393627343</v>
+        <v>0.0677903254953046</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1503</v>
+        <v>1417</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>145.0532560491718</v>
+        <v>157.4545696507094</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>196</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.31217133437794</v>
+        <v>46.78550203855796</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>8.732597075688803</v>
+        <v>23.48663002731823</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.9085331368008336</v>
+        <v>1.191606764802882</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0994439746222799</v>
+        <v>0.018253408912437</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1466</v>
+        <v>1435</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>144.3775124002751</v>
+        <v>148.2684549892786</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>14.35</v>
+        <v>21.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>30.87512028404005</v>
+        <v>49.6365823558094</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.7314205512319</v>
+        <v>6.797353847115616</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.170238334356761</v>
+        <v>0.9753150353875368</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0138135332090664</v>
+        <v>0.1922640061232636</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1229</v>
+        <v>1530</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>142.3407797347815</v>
+        <v>146.0196992075363</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>39.65</v>
+        <v>26.7</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.71250068867732</v>
+        <v>36.87335917952693</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.61136641516342</v>
+        <v>21.12722710238842</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.9912750295218736</v>
+        <v>0.9660150962722694</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0592587555237908</v>
+        <v>-0.0100445393516075</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1512</v>
+        <v>1466</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>142.1466543715215</v>
+        <v>144.3775124002751</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>6.22</v>
+        <v>14.35</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.76372751561494</v>
+        <v>30.87512035524826</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.831952736275399</v>
+        <v>12.7314205512319</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5014464145161638</v>
+        <v>1.170238334356761</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0167017029959682</v>
+        <v>-0.0138135331979392</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1438</v>
+        <v>1512</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>136.9848893759074</v>
+        <v>142.1466543715215</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>21.5</v>
+        <v>6.22</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>45.89683355749976</v>
+        <v>45.76372729045306</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9.119143729849148</v>
+        <v>9.831952848864956</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.8625454013007244</v>
+        <v>0.5014464145161638</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0042681897894382</v>
+        <v>0.0167017030315755</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1522</v>
+        <v>1438</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>106.472265489854</v>
+        <v>136.9848893759075</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>25.75</v>
+        <v>21.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>38.05280417543786</v>
+        <v>45.89683357679721</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.6205907540172</v>
+        <v>9.11914374626793</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.9820103202713192</v>
+        <v>0.8625454013007244</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0833751467911889</v>
+        <v>-0.0042681898339478</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1325</v>
+        <v>1522</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>102.5508377839253</v>
+        <v>126.472265489854</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>25.7</v>
+        <v>25.75</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.14818284654244</v>
+        <v>38.05280360495686</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.50328483890042</v>
+        <v>18.62059108808068</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.139476877717596</v>
+        <v>0.9820103202713192</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.027348461416319</v>
+        <v>0.083375147291906</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1219</v>
+        <v>1432</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>101.0408449471228</v>
+        <v>109.5077726614187</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>11.2</v>
+        <v>14.95</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>41.91031107278293</v>
+        <v>43.48163136233596</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>15.01605990971647</v>
+        <v>10.56259224900865</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.334772340492953</v>
+        <v>0.812690453738681</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0152550318449268</v>
+        <v>0.0049427769677399</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1445</v>
+        <v>1219</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>99.27339776686875</v>
+        <v>101.0408449471228</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9.98</v>
+        <v>11.2</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>39.99733213516019</v>
+        <v>41.91031109590691</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.32646286746622</v>
+        <v>15.01605991173722</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.254008309959897</v>
+        <v>1.334772340492953</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0014068641370873</v>
+        <v>-0.0152550318671825</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1452</v>
+        <v>1445</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>95.13262548194982</v>
+        <v>99.27339776686878</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>10.6</v>
+        <v>9.98</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>29.68446946442156</v>
+        <v>39.99733251275112</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.96596610792764</v>
+        <v>11.32646288345266</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.45241420740407</v>
+        <v>1.254008309959897</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0169626983658678</v>
+        <v>-0.0014068641148333</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1432</v>
+        <v>1452</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>89.50777266141873</v>
+        <v>95.1326254819498</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>14.95</v>
+        <v>10.6</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>43.48163148472762</v>
+        <v>29.68446946442156</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>10.56259224900865</v>
+        <v>18.965966122662</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.812690453738681</v>
+        <v>1.45241420740407</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0049427769677399</v>
+        <v>-0.0169626983658678</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>44.67391105333945</v>
+        <v>44.67391092409282</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>10.42596316676628</v>
+        <v>10.42596317095857</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.6713898791149702</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0599419466973581</v>
+        <v>0.0599419467863765</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>41.98291997872475</v>
+        <v>41.98292004778726</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>10.08824348559902</v>
+        <v>10.08824345937464</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.871470302379391</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0405682985111746</v>
+        <v>-0.0405682985000457</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>77.69909659555569</v>
+        <v>77.69909659559642</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>12.05</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>38.15402494387296</v>
+        <v>38.1540250324549</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>19.57847090452008</v>
+        <v>19.57847091734101</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.6956808685531496</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0389864704367821</v>
+        <v>-0.038986470447909</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>51.99558286604059</v>
+        <v>51.99558286604143</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>63.3</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>50.62024391115403</v>
+        <v>50.62024390837107</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>15.85678167396862</v>
+        <v>15.85678159109072</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.3920305985933084</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.8830948080154633</v>
+        <v>0.8830948082157417</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq1_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-05.xlsx
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1326</v>
+        <v>1569</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>955.5074210307712</v>
+        <v>963.2329512120886</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>59.82798828216806</v>
+        <v>78.29839855836863</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.49140989435775</v>
+        <v>59.96617862328991</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.9988176158365332</v>
+        <v>1.923295121208853</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.08605308859099201</v>
+        <v>0.9831704391127448</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1569</v>
+        <v>1326</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>933.2329512120886</v>
+        <v>955.5074210307712</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>78.29839855836863</v>
+        <v>59.82798828216806</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>59.96617862328991</v>
+        <v>28.49140989435775</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.923295121208853</v>
+        <v>0.9988176158365332</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.9831704391127448</v>
+        <v>0.08605308859099201</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
